--- a/workbooks/chi-steward-workbook.xlsx
+++ b/workbooks/chi-steward-workbook.xlsx
@@ -16580,7 +16580,7 @@
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
+          <t>Ajay Prashar</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
+          <t>Ajay Prashar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
+          <t>Ajay Prashar</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
+          <t>Ajay Prashar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
+          <t>Ajay Prashar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18942,8 +18942,8 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
@@ -19396,10 +19396,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>Ajay Prashar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ajay.Prashar@acgov.org</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -19459,10 +19463,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>Ajay Prashar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ajay.Prashar@acgov.org</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -19565,10 +19573,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>Ajay Prashar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Ajay.Prashar@acgov.org</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -19628,10 +19640,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>Ajay Prashar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ajay.Prashar@acgov.org</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -19691,10 +19707,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SHIE Data Governance</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>Ajay Prashar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ajay.Prashar@acgov.org</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>Approved</t>

--- a/workbooks/chi-steward-workbook.xlsx
+++ b/workbooks/chi-steward-workbook.xlsx
@@ -18,9 +18,12 @@
     <sheet name="CCDA_Mappings" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="FHIR_Inventory" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Business_Rules" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Source_Registry" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Steward_Queue" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Concept_Explorer" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Value_Set_Bindings" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Value_Set_Members" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Source_Value_Crosswalk" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Source_Registry" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Steward_Queue" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Concept_Explorer" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -178,8 +181,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="chi_table_index" displayName="chi_table_index" ref="A1:D13" headerRowCount="1">
-  <autoFilter ref="A1:D13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="chi_table_index" displayName="chi_table_index" ref="A1:D16" headerRowCount="1">
+  <autoFilter ref="A1:D16"/>
   <tableColumns count="4">
     <tableColumn id="1" name="excel_table_name"/>
     <tableColumn id="2" name="sheet_tab"/>
@@ -191,7 +194,68 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="chi_source_registry" displayName="chi_source_registry" ref="A1:E2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="chi_value_set_binding" displayName="chi_value_set_binding" ref="A1:K6" headerRowCount="1">
+  <autoFilter ref="A1:K6"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="semantic_id"/>
+    <tableColumn id="2" name="binding_role"/>
+    <tableColumn id="3" name="value_set_name"/>
+    <tableColumn id="4" name="value_set_url"/>
+    <tableColumn id="5" name="code_system_oid"/>
+    <tableColumn id="6" name="code_system_name"/>
+    <tableColumn id="7" name="binding_strength"/>
+    <tableColumn id="8" name="fhir_element"/>
+    <tableColumn id="9" name="authority_reference"/>
+    <tableColumn id="10" name="approval_status"/>
+    <tableColumn id="11" name="notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="chi_value_set_member" displayName="chi_value_set_member" ref="A1:J22" headerRowCount="1">
+  <autoFilter ref="A1:J22"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="semantic_id"/>
+    <tableColumn id="2" name="code_system_oid"/>
+    <tableColumn id="3" name="code"/>
+    <tableColumn id="4" name="display"/>
+    <tableColumn id="5" name="member_type"/>
+    <tableColumn id="6" name="binding_role"/>
+    <tableColumn id="7" name="binding_strength"/>
+    <tableColumn id="8" name="active"/>
+    <tableColumn id="9" name="sort_order"/>
+    <tableColumn id="10" name="notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="chi_source_value_crosswalk" displayName="chi_source_value_crosswalk" ref="A1:M5" headerRowCount="1">
+  <autoFilter ref="A1:M5"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="source_id"/>
+    <tableColumn id="2" name="source_field"/>
+    <tableColumn id="3" name="source_code"/>
+    <tableColumn id="4" name="source_display"/>
+    <tableColumn id="5" name="semantic_id"/>
+    <tableColumn id="6" name="target_code_system_oid"/>
+    <tableColumn id="7" name="target_code"/>
+    <tableColumn id="8" name="target_display"/>
+    <tableColumn id="9" name="mapping_type"/>
+    <tableColumn id="10" name="approval_status"/>
+    <tableColumn id="11" name="effective_from"/>
+    <tableColumn id="12" name="effective_to"/>
+    <tableColumn id="13" name="notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="chi_source_registry" displayName="chi_source_registry" ref="A1:E2" headerRowCount="1">
   <autoFilter ref="A1:E2"/>
   <tableColumns count="5">
     <tableColumn id="1" name="source_id"/>
@@ -204,8 +268,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="chi_steward_queue" displayName="chi_steward_queue" ref="A1:H47" headerRowCount="1">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="chi_steward_queue" displayName="chi_steward_queue" ref="A1:H47" headerRowCount="1">
   <autoFilter ref="A1:H47"/>
   <tableColumns count="8">
     <tableColumn id="1" name="semantic_id"/>
@@ -16509,6 +16573,1878 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>semantic_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>binding_role</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>value_set_name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>value_set_url</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>code_system_oid</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>code_system_name</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>binding_strength</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>fhir_element</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>authority_reference</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>approval_status</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HL7 Race</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/ValueSet/v3-Race</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CDCREC</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Patient.extension(us-core-race).ombCategory</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>docs/shie-standards-reference.md#cdcrec-race-codes-omb-rollup-examples</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>US Core us-core-race: ombCategory required; detailed optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HL7 Ethnicity</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/ValueSet/v3-Ethnicity</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CDCREC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Patient.extension(us-core-ethnicity).ombCategory</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>docs/shie-standards-reference.md#cdcrec-ethnicity-codes-examples</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>US Core us-core-ethnicity extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FHIR Languages (BCP 47)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/ValueSet/languages</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BCP 47</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Patient.communication.language</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>docs/shie-standards-reference.md</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Primary FHIR binding; ISO 639 for stewardship crosswalk only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Patient.gender_id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>US Core Gender Identity Observation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-social-history</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LOINC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Observation.code (LOINC 76691-5)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>docs/shie-standards-reference.md</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Answer values often SNOMED-coded; expand members from US Core / partner intake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>US Core Birth Sex</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-birthsex</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>US Core birth sex</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Patient.extension(us-core-birthsex)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>docs/shie-standards-reference.md</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Administrative sex — not CDCREC; distinct from gender identity.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>semantic_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>code_system_oid</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>display</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>member_type</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>binding_role</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>binding_strength</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1002-5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>American Indian or Alaska Native</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>omb_rollup</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>HL7 Race Value Set / CDC PHIN reporting rollup</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2028-9</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>omb_rollup</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>HL7 Race Value Set / CDC PHIN reporting rollup</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2054-5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Black or African American</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>omb_rollup</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>HL7 Race Value Set / CDC PHIN reporting rollup</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2076-8</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>omb_rollup</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>HL7 Race Value Set / CDC PHIN reporting rollup</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2106-3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>omb_rollup</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>HL7 Race Value Set / CDC PHIN reporting rollup</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2131-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Other Race</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>omb_rollup</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>HL7 Race Value Set / CDC PHIN reporting rollup</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.5.1008</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>nullflavor</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nullflavor</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Do not collapse with valid race codes in reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.5.1008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ASKU</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Asked but not known</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>nullflavor</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nullflavor</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Do not collapse with valid race codes in reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.5.1008</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NASK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Not asked</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>nullflavor</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>nullflavor</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Do not collapse with valid race codes in reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>omb_rollup</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2186-5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Not Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>omb_rollup</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.5.1008</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>nullflavor</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nullflavor</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Distinct from patient-refused / declined in survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>language_tag</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pilot examples; full list from IANA/BCP 47 — not duplicated locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>language_tag</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Pilot examples; full list from IANA/BCP 47 — not duplicated locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>language_tag</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Pilot examples; full list from IANA/BCP 47 — not duplicated locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>language_tag</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Pilot examples; full list from IANA/BCP 47 — not duplicated locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>language_tag</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Pilot examples; full list from IANA/BCP 47 — not duplicated locally</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>administrative</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Not interchangeable with Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>administrative</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Not interchangeable with Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>administrative</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Not interchangeable with Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>source_field</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>source_code</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>source_display</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>semantic_id</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>target_code_system_oid</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>target_code</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>target_display</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>mapping_type</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>approval_status</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>effective_from</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>effective_to</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cmt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PID-10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EXAMPLE_B</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CMT race code (replace with validated list)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2054-5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Black or African American</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>POC placeholder — populate from CMT race code inventory / county Table 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cmt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PID-22</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EXAMPLE_H</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CMT ethnicity code (replace with validated list)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>POC placeholder — populate from CMT ethnicity code inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cmt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PID-15</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Example exact map when CMT sends BCP 47 or ISO-aligned language code</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cmt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PID-8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Administrative sex / SexID — not gender identity</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16569,7 +18505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17402,13 +19338,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -17599,21 +19535,54 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Governed code (first member)</t>
+        </is>
+      </c>
+      <c r="B18" s="2">
+        <f>IF($B$3="","",IFERROR(INDEX(chi_value_set_member[code],MATCH($B$3,chi_value_set_member[semantic_id],0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Governed code display (first member)</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <f>IF($B$3="","",IFERROR(INDEX(chi_value_set_member[display],MATCH($B$3,chi_value_set_member[semantic_id],0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Source crosswalk code (first match)</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <f>IF($B$3="","",IFERROR(INDEX(chi_source_value_crosswalk[source_code],MATCH($B$3,chi_source_value_crosswalk[semantic_id],0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Primary source (first link)</t>
         </is>
       </c>
-      <c r="B18" s="2">
+      <c r="B21" s="2">
         <f>IF($B$3="","",IFERROR(INDEX(chi_source_availability[source_id],MATCH($B$3,chi_source_availability[semantic_id],0)),""))</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Source availability</t>
         </is>
       </c>
-      <c r="B19" s="2">
+      <c r="B22" s="2">
         <f>IF($B$3="","",IFERROR(INDEX(chi_source_availability[availability],MATCH($B$3,chi_source_availability[semantic_id],0)),""))</f>
         <v/>
       </c>
@@ -17629,13 +19598,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
@@ -17903,35 +19872,146 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>catalog_value_set_binding</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>chi_catalog</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>semantic_id</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>chi_value_set_binding</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>semantic_id</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1:N</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Which terminology / value set applies to the concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>catalog_value_set_member</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>chi_catalog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>semantic_id</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>chi_value_set_member</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>semantic_id</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1:N</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Governed codes for the concept (CHI subset).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>catalog_source_crosswalk</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>chi_catalog</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>semantic_id</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>chi_source_value_crosswalk</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>semantic_id</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1:N</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Source-local values mapped to governed standard codes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>catalog_steward_queue</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>chi_catalog</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>semantic_id</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>chi_steward_queue</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>semantic_id</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Optional steward workflow overlay keyed by semantic_id.</t>
         </is>
@@ -17948,11 +20028,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -18202,42 +20282,108 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>chi_lookup_lists</t>
+          <t>chi_value_set_binding</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lookup_Lists</t>
+          <t>Value_Set_Bindings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(reference lists)</t>
+          <t>ddc-value_set_binding.parquet</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Terminology</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>chi_value_set_member</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Value_Set_Members</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ddc-value_set_member.parquet</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Terminology</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>chi_source_value_crosswalk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Source_Value_Crosswalk</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ddc-source_value_crosswalk.parquet</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Crosswalk</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chi_lookup_lists</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lookup_Lists</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>(reference lists)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>chi_table_index</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Table_Index</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>(navigation map; not imported)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>

--- a/workbooks/chi-steward-workbook.xlsx
+++ b/workbooks/chi-steward-workbook.xlsx
@@ -233,8 +233,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="chi_source_value_crosswalk" displayName="chi_source_value_crosswalk" ref="A1:M5" headerRowCount="1">
-  <autoFilter ref="A1:M5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="chi_source_value_crosswalk" displayName="chi_source_value_crosswalk" ref="A1:M111" headerRowCount="1">
+  <autoFilter ref="A1:M111"/>
   <tableColumns count="13">
     <tableColumn id="1" name="source_id"/>
     <tableColumn id="2" name="source_field"/>
@@ -65698,17 +65698,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -65786,22 +65786,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cmt</t>
+          <t>county_master</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PID-10</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EXAMPLE_B</t>
+          <t>African American</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CMT race code (replace with validated list)</t>
+          <t>African American</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -65838,34 +65838,34 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>POC placeholder — populate from CMT race code inventory / county Table 5</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cmt</t>
+          <t>county_master</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PID-22</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EXAMPLE_H</t>
+          <t>American Indian</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CMT ethnicity code (replace with validated list)</t>
+          <t>American Indian</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Patient.ethnicity</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -65875,12 +65875,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2135-2</t>
+          <t>1002-5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hispanic or Latino</t>
+          <t>American Indian or Alaska Native</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -65897,54 +65897,54 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>POC placeholder — populate from CMT ethnicity code inventory</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cmt</t>
+          <t>county_master</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PID-15</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>American Indian or Alaska Native</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>American Indian or Alaska Native</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Patient.language</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>urn:ietf:bcp:47</t>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>1002-5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>American Indian or Alaska Native</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -65956,54 +65956,54 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Example exact map when CMT sends BCP 47 or ISO-aligned language code</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cmt</t>
+          <t>county_master</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PID-8</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2028-9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -66015,7 +66015,6133 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Administrative sex / SexID — not gender identity</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Asian /White</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Asian /White</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2131-1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Other Race</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Asian Indian</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Asian Indian</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2028-9</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2054-5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Black or African American</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Black or African American</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Black or African American</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2054-5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Black or African American</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Black Or African American /White</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Black Or African American /White</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2131-1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Other Race</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cambodian</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cambodian</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2028-9</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CAUCASIAN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CAUCASIAN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2106-3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2028-9</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Eskimo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Eskimo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1002-5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>American Indian or Alaska Native</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Filipino</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Filipino</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2028-9</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Guamanian or Chamorro</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Guamanian or Chamorro</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076-8</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2028-9</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2028-9</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Laotian</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Laotian</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2028-9</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>More than one race</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>More than one race</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2131-1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Other Race</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NAT AMER/ESK/ALEUT</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NAT AMER/ESK/ALEUT</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1002-5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>American Indian or Alaska Native</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Native American/Alaskan / White</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Native American/Alaskan / White</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2131-1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Other Race</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Native American/Alaskan /Black</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Native American/Alaskan /Black</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2131-1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Other Race</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Native Hawaiian</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Native Hawaiian</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2076-8</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2076-8</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2076-8</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Samoan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Samoan</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2076-8</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2028-9</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2106-3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Unknown/Not Reported</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Unknown/Not Reported</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DTS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DTS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Other Race</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Other Race</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cuban</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cuban</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mexican</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Mexicano</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Mexicano</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NOT HISPANIC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NOT HISPANIC</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2186-5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Not Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Not Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Not Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2186-5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Not Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Puerto Rican</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Puerto Rican</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Declined To Specify</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Declined To Specify</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MU Unknown Do Not Use</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MU Unknown Do Not Use</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Patient Refused</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Patient Refused</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Unk/Decline</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Unk/Decline</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ethnicity</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Patient.ethnicity</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>spa</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>vie</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>jpn</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>zho</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ara</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Arabic</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hin</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>rus</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ru</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ru</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>nld</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Dutch</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>nl</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Dutch</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>mya</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Burmese</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Burmese</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Burmese</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Burmese</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>my</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Burmese</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>tir</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ti</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ti</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tigrinya</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ti</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>tgl</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>tl</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>tl</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Mam</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mam</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>mam</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Mam</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Cantonese</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Cantonese</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>yue</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Cantonese</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Mandarin</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Mandarin</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>cmn</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Mandarin</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Thai</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Thai</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>th</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Thai</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Persian</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Persian</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>fa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Persian</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Farsi</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Farsi</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>fa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Farsi</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Hebrew</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Hebrew</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>he</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Hebrew</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>so</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Amharic</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Amharic</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>am</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Amharic</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Bengali</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Bengali</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bengali</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Gujarati</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Gujarati</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>gu</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Gujarati</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Urdu</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Urdu</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ur</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Urdu</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Lao</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Lao</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>lo</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Lao</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Laotian</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Laotian</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>lo</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Laotian</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Cambodian</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Cambodian</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Cambodian</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Armenian</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Armenian</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>hy</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Armenian</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ASL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sign language</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>sgn</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sign language</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Sign Language</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sign language</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>sgn</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sign language</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sgn</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sign Language</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>sgn</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sign Language</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates; und excluded per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Declined to specify</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Declined to specify</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates; und excluded per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Declined to spec</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Declined to spec</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates; und excluded per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates; und excluded per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates; und excluded per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates; und excluded per survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Male to Female</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Male to Female</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Female to Male</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Female to Male</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Treated as null at master level per county SexID logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Treated as null at master level per county SexID logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Treated as null at master level per county SexID logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Unknown/ Other</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Unknown/ Other</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Treated as null at master level per county SexID logic</t>
         </is>
       </c>
     </row>

--- a/workbooks/chi-steward-workbook.xlsx
+++ b/workbooks/chi-steward-workbook.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="_Model" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Table_Index" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lookup_Lists" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Catalog" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Dictionary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Source_Availability" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ADT_Mappings" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CCDA_Mappings" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="FHIR_Inventory" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Business_Rules" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Value_Set_Bindings" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Value_Set_Members" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Source_Value_Crosswalk" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Source_Registry" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Steward_Queue" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Concept_Explorer" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Model" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table_Index" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookup_Lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Availability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADT_Mappings" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCDA_Mappings" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FHIR_Inventory" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business_Rules" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value_Set_Bindings" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value_Set_Members" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Value_Crosswalk" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Registry" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steward_Queue" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concept_Explorer" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -233,8 +233,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="chi_source_value_crosswalk" displayName="chi_source_value_crosswalk" ref="A1:M111" headerRowCount="1">
-  <autoFilter ref="A1:M111"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="chi_source_value_crosswalk" displayName="chi_source_value_crosswalk" ref="A1:M187" headerRowCount="1">
+  <autoFilter ref="A1:M187"/>
   <tableColumns count="13">
     <tableColumn id="1" name="source_id"/>
     <tableColumn id="2" name="source_field"/>
@@ -65698,7 +65698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -65831,14 +65831,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -65890,14 +65890,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -65949,14 +65949,14 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66008,14 +66008,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66067,14 +66067,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66091,12 +66091,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Asian Indian</t>
+          <t>Asian/ White</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Asian Indian</t>
+          <t>Asian/ White</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -66111,12 +66111,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2028-9</t>
+          <t>2131-1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Asian</t>
+          <t>Other Race</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -66126,14 +66126,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66150,12 +66150,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian Indian</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian Indian</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -66170,12 +66170,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2054-5</t>
+          <t>2028-9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Black or African American</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -66185,14 +66185,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66209,34 +66209,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Patient.race</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2054-5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>Black or African American</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Black or African American</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Patient.race</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>urn:oid:2.16.840.1.113883.6.238</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2054-5</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Black or African American</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>rollup</t>
@@ -66244,14 +66244,14 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66268,12 +66268,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Black Or African American /White</t>
+          <t>Black or African American</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Black Or African American /White</t>
+          <t>Black or African American</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -66288,12 +66288,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2131-1</t>
+          <t>2054-5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Other Race</t>
+          <t>Black or African American</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -66303,14 +66303,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66327,12 +66327,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cambodian</t>
+          <t>Black Or African American /White</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cambodian</t>
+          <t>Black Or African American /White</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -66347,12 +66347,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2028-9</t>
+          <t>2131-1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Asian</t>
+          <t>Other Race</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -66362,14 +66362,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66386,12 +66386,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CAUCASIAN</t>
+          <t>Black Or African American/ White</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CAUCASIAN</t>
+          <t>Black Or African American/ White</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -66406,12 +66406,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2106-3</t>
+          <t>2131-1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Other Race</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -66421,14 +66421,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66445,12 +66445,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Cambodian</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Cambodian</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -66480,14 +66480,14 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66504,12 +66504,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eskimo</t>
+          <t>CAUCASIAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Eskimo</t>
+          <t>CAUCASIAN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -66524,12 +66524,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1002-5</t>
+          <t>2106-3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>American Indian or Alaska Native</t>
+          <t>White</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -66539,14 +66539,14 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66563,12 +66563,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Causasian</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Causasian</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -66583,12 +66583,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2028-9</t>
+          <t>2106-3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Asian</t>
+          <t>White</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -66598,14 +66598,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66622,12 +66622,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Guamanian or Chamorro</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Guamanian or Chamorro</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -66642,12 +66642,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2076-8</t>
+          <t>2028-9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Native Hawaiian or Other Pacific Islander</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -66657,14 +66657,14 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66681,12 +66681,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>DTS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>DTS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -66699,31 +66699,23 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2028-9</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Asian</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>rollup</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -66740,12 +66732,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>Eskimo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>Eskimo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -66760,12 +66752,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2028-9</t>
+          <t>1002-5</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Asian</t>
+          <t>American Indian or Alaska Native</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -66775,14 +66767,14 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66799,12 +66791,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Laotian</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Laotian</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -66834,14 +66826,14 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66858,12 +66850,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>More than one race</t>
+          <t>Guamanian or Chamorro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>More than one race</t>
+          <t>Guamanian or Chamorro</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -66878,12 +66870,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2131-1</t>
+          <t>2076-8</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Other Race</t>
+          <t>Native Hawaiian or Other Pacific Islander</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -66893,14 +66885,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66917,12 +66909,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NAT AMER/ESK/ALEUT</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NAT AMER/ESK/ALEUT</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -66937,12 +66929,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1002-5</t>
+          <t>2028-9</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>American Indian or Alaska Native</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -66952,14 +66944,14 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -66976,12 +66968,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Native American/Alaskan / White</t>
+          <t>Korean</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Native American/Alaskan / White</t>
+          <t>Korean</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -66996,12 +66988,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2131-1</t>
+          <t>2028-9</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Other Race</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -67011,14 +67003,14 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67035,12 +67027,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Native American/Alaskan /Black</t>
+          <t>Laotian</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Native American/Alaskan /Black</t>
+          <t>Laotian</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -67055,12 +67047,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2131-1</t>
+          <t>2028-9</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Other Race</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -67070,14 +67062,14 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67094,12 +67086,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Native Hawaiian</t>
+          <t>More than one race</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Native Hawaiian</t>
+          <t>More than one race</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -67114,12 +67106,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2076-8</t>
+          <t>2131-1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Native Hawaiian or Other Pacific Islander</t>
+          <t>Other Race</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -67129,14 +67121,14 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67153,12 +67145,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Native Hawaiian or Other Pacific Islander</t>
+          <t>NAT AMER/ESK/ALEUT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Native Hawaiian or Other Pacific Islander</t>
+          <t>NAT AMER/ESK/ALEUT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -67173,12 +67165,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2076-8</t>
+          <t>1002-5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Native Hawaiian or Other Pacific Islander</t>
+          <t>American Indian or Alaska Native</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -67188,14 +67180,14 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67212,12 +67204,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other Pacific Islander</t>
+          <t>Nat Amer/Esk/Aleut</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Other Pacific Islander</t>
+          <t>Nat Amer/Esk/Aleut</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -67232,12 +67224,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2076-8</t>
+          <t>1002-5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Native Hawaiian or Other Pacific Islander</t>
+          <t>American Indian or Alaska Native</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -67247,14 +67239,14 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67271,12 +67263,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Samoan</t>
+          <t>Native American/Alaskan / White</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Samoan</t>
+          <t>Native American/Alaskan / White</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -67291,12 +67283,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2076-8</t>
+          <t>2131-1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Native Hawaiian or Other Pacific Islander</t>
+          <t>Other Race</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -67306,14 +67298,14 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67330,12 +67322,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnamese</t>
+          <t>Native American/Alaskan /Black</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vietnamese</t>
+          <t>Native American/Alaskan /Black</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -67350,12 +67342,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2028-9</t>
+          <t>2131-1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Asian</t>
+          <t>Other Race</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -67365,14 +67357,14 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67389,12 +67381,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Native American/ Alaskan/ White</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Native American/ Alaskan/ White</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -67409,12 +67401,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2106-3</t>
+          <t>2131-1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Other Race</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -67424,14 +67416,14 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67448,12 +67440,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Native American/ Alaskan/ Black</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Native American/ Alaskan/ Black</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -67466,23 +67458,31 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2131-1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Other Race</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67499,12 +67499,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Native Hawaiian</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Native Hawaiian</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -67517,23 +67517,31 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2076-8</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67550,12 +67558,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Unknown/Not Reported</t>
+          <t>Native Hawaiian or Other Pacific Islander</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Unknown/Not Reported</t>
+          <t>Native Hawaiian or Other Pacific Islander</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -67568,23 +67576,31 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2076-8</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67601,12 +67617,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DTS</t>
+          <t>Other Pacific Islander</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DTS</t>
+          <t>Other Pacific Islander</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -67619,23 +67635,31 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2076-8</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Native Hawaiian or Other Pacific Islander</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67679,14 +67703,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -67698,22 +67722,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ethnicity</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cuban</t>
+          <t>Samoan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cuban</t>
+          <t>Samoan</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Patient.ethnicity</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -67723,12 +67747,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2135-2</t>
+          <t>2076-8</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Hispanic or Latino</t>
+          <t>Native Hawaiian or Other Pacific Islander</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -67738,14 +67762,14 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -67757,22 +67781,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ethnicity</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hispanic or Latino</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Hispanic or Latino</t>
+          <t>U</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Patient.ethnicity</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -67780,31 +67804,23 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2135-2</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Hispanic or Latino</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>rollup</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -67816,22 +67832,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ethnicity</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mexican</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mexican</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Patient.ethnicity</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -67839,31 +67855,23 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2135-2</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Hispanic or Latino</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>rollup</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -67875,22 +67883,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ethnicity</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mexicano</t>
+          <t>Unknown/Not Reported</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mexicano</t>
+          <t>Unknown/Not Reported</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Patient.ethnicity</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -67898,31 +67906,23 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2135-2</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Hispanic or Latino</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>rollup</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -67934,22 +67934,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ethnicity</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NOT HISPANIC</t>
+          <t>Unknown/ Not Reported</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NOT HISPANIC</t>
+          <t>Unknown/ Not Reported</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Patient.ethnicity</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -67957,31 +67957,23 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2186-5</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Not Hispanic or Latino</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>rollup</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -67993,22 +67985,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ethnicity</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Not Hispanic or Latino</t>
+          <t>Vietnamese</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Not Hispanic or Latino</t>
+          <t>Vietnamese</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Patient.ethnicity</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -68018,12 +68010,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2186-5</t>
+          <t>2028-9</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Not Hispanic or Latino</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -68033,14 +68025,14 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68052,22 +68044,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ethnicity</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Puerto Rican</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Puerto Rican</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Patient.ethnicity</t>
+          <t>Patient.race</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -68077,12 +68069,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2135-2</t>
+          <t>2106-3</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Hispanic or Latino</t>
+          <t>White</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -68092,14 +68084,14 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 race groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68116,12 +68108,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Declined To Specify</t>
+          <t>Cuban</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Declined To Specify</t>
+          <t>Cuban</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -68134,23 +68126,31 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68167,12 +68167,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MU Unknown Do Not Use</t>
+          <t>Declined To Specify</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MU Unknown Do Not Use</t>
+          <t>Declined To Specify</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -68194,14 +68194,14 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -68218,12 +68218,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Patient Refused</t>
+          <t>Hispanic or Latino</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Patient Refused</t>
+          <t>Hispanic or Latino</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -68236,23 +68236,31 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68269,12 +68277,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unk/Decline</t>
+          <t>Mexican</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Unk/Decline</t>
+          <t>Mexican</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -68287,23 +68295,31 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68320,12 +68336,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mexicano</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mexicano</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -68338,23 +68354,31 @@
           <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2135-2</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Hispanic or Latino</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68366,54 +68390,46 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>MU Unknown Do Not Use</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>MU Unknown Do Not Use</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Patient.language</t>
+          <t>Patient.ethnicity</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>urn:ietf:bcp:47</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -68425,54 +68441,54 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>NOT HISPANIC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>NOT HISPANIC</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Patient.language</t>
+          <t>Patient.ethnicity</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>urn:ietf:bcp:47</t>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>2186-5</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Not Hispanic or Latino</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68484,54 +68500,54 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>spa</t>
+          <t>Not Hispanic</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Not Hispanic</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Patient.language</t>
+          <t>Patient.ethnicity</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>urn:ietf:bcp:47</t>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>es</t>
+          <t>2186-5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Not Hispanic or Latino</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68543,54 +68559,54 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Not Hispanic or Latino</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Not Hispanic or Latino</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Patient.language</t>
+          <t>Patient.ethnicity</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>urn:ietf:bcp:47</t>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>es</t>
+          <t>2186-5</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Not Hispanic or Latino</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68602,54 +68618,46 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>vie</t>
+          <t>Patient Refused</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Vietnamese</t>
+          <t>Patient Refused</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Patient.language</t>
+          <t>Patient.ethnicity</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>urn:ietf:bcp:47</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>vi</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Vietnamese</t>
-        </is>
-      </c>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -68661,54 +68669,54 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Vietnamese</t>
+          <t>Puerto Rican</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Vietnamese</t>
+          <t>Puerto Rican</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Patient.language</t>
+          <t>Patient.ethnicity</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>urn:ietf:bcp:47</t>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>vi</t>
+          <t>2135-2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Vietnamese</t>
+          <t>Hispanic or Latino</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rollup</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 5 ethnicity groupings → CDCREC OMB</t>
         </is>
       </c>
     </row>
@@ -68720,54 +68728,46 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jpn</t>
+          <t>Unk/Decline</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Unk/Decline</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Patient.language</t>
+          <t>Patient.ethnicity</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>urn:ietf:bcp:47</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Japanese</t>
-        </is>
-      </c>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -68779,54 +68779,46 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Ethnicity</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Patient.language</t>
+          <t>Patient.ethnicity</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>urn:ietf:bcp:47</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Japanese</t>
-        </is>
-      </c>
+          <t>urn:oid:2.16.840.1.113883.6.238</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>Excluded from county aggregates per Table 5 survivorship</t>
         </is>
       </c>
     </row>
@@ -68843,12 +68835,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>zho</t>
+          <t>Achinese</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Achinese</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -68863,12 +68855,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>ace</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Achinese</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -68878,14 +68870,14 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -68902,12 +68894,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Abkhazian</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Abkhazian</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -68922,12 +68914,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Abkhazian</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -68937,14 +68929,14 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -68961,12 +68953,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ara</t>
+          <t>Afrikaans</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Afrikaans</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -68981,12 +68973,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>af</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Afrikaans</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -68996,14 +68988,14 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69020,12 +69012,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Albanian</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Albanian</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -69040,12 +69032,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>sq</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Albanian</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -69055,14 +69047,14 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69079,12 +69071,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>hin</t>
+          <t>Amharic</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Amharic</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -69099,12 +69091,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>hi</t>
+          <t>am</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Amharic</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -69114,14 +69106,14 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69138,12 +69130,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -69158,12 +69150,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>hi</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -69173,14 +69165,14 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69197,12 +69189,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>rus</t>
+          <t>ara</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Russian</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -69217,12 +69209,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ru</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Russian</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -69232,14 +69224,14 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69256,12 +69248,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russian</t>
+          <t>Armenian</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Russian</t>
+          <t>Armenian</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -69276,12 +69268,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ru</t>
+          <t>hy</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Russian</t>
+          <t>Armenian</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -69291,14 +69283,14 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69315,12 +69307,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>nld</t>
+          <t>ASL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Dutch</t>
+          <t>Sign language</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -69335,12 +69327,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>ase</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Dutch</t>
+          <t>Sign language</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -69350,14 +69342,14 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69374,12 +69366,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>mya</t>
+          <t>Basque</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Burmese</t>
+          <t>Basque</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -69394,12 +69386,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>eu</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Burmese</t>
+          <t>Basque</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -69409,14 +69401,14 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69433,12 +69425,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Burmese</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Burmese</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -69453,12 +69445,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>bn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Burmese</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -69468,14 +69460,14 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69492,12 +69484,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>tir</t>
+          <t>Berber (Other)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tigrigna</t>
+          <t>Berber</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -69512,12 +69504,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ti</t>
+          <t>ber</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tigrigna</t>
+          <t>Berber</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -69527,14 +69519,14 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69551,12 +69543,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tigrigna</t>
+          <t>Bosnian</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tigrigna</t>
+          <t>Bosnian</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -69571,12 +69563,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ti</t>
+          <t>bs</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tigrigna</t>
+          <t>Bosnian</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -69586,14 +69578,14 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69610,12 +69602,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tigrinya</t>
+          <t>Bulgarian</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tigrigna</t>
+          <t>Bulgarian</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -69630,12 +69622,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ti</t>
+          <t>bg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tigrigna</t>
+          <t>Bulgarian</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -69645,14 +69637,14 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69669,12 +69661,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>tgl</t>
+          <t>Burmese</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tagalog</t>
+          <t>Burmese</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -69689,12 +69681,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>tl</t>
+          <t>my</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tagalog</t>
+          <t>Burmese</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -69704,14 +69696,14 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69728,12 +69720,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tagalog</t>
+          <t>mya</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tagalog</t>
+          <t>Burmese</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -69748,12 +69740,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>tl</t>
+          <t>my</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tagalog</t>
+          <t>Burmese</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -69763,14 +69755,14 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69787,12 +69779,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mam</t>
+          <t>Cambodian</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mam</t>
+          <t>Cambodian</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -69807,12 +69799,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>mam</t>
+          <t>km</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Mam</t>
+          <t>Cambodian</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -69822,14 +69814,14 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69846,12 +69838,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cantonese</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cantonese</t>
+          <t>Cemuhî</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -69866,12 +69858,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>yue</t>
+          <t>cam</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Cantonese</t>
+          <t>Cemuhî</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -69881,14 +69873,14 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69905,12 +69897,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Cantonese</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Cantonese</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -69925,12 +69917,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>cmn</t>
+          <t>yue</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Cantonese</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -69940,14 +69932,14 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -69964,12 +69956,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>Catalan; Valencian</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>Catalan; Valencian</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -69984,12 +69976,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>Catalan; Valencian</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -69999,14 +69991,14 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70023,12 +70015,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thai</t>
+          <t>Central Khmer</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Thai</t>
+          <t>Central Khmer</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -70043,12 +70035,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>km</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Thai</t>
+          <t>Central Khmer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -70058,14 +70050,14 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70082,12 +70074,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -70102,12 +70094,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -70117,14 +70109,14 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70141,12 +70133,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>zho</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -70161,12 +70153,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -70176,14 +70168,14 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70200,12 +70192,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portuguese</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Portuguese</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -70220,12 +70212,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Portuguese</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -70235,14 +70227,14 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70259,12 +70251,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Persian</t>
+          <t>Croatian</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Persian</t>
+          <t>Croatian</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -70279,12 +70271,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>fa</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Persian</t>
+          <t>Croatian</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -70294,14 +70286,14 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70318,12 +70310,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Farsi</t>
+          <t>Danish</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Farsi</t>
+          <t>Danish</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -70338,12 +70330,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>fa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Farsi</t>
+          <t>Danish</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -70353,14 +70345,14 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70377,12 +70369,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hebrew</t>
+          <t>Dari</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Hebrew</t>
+          <t>Dari</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -70397,12 +70389,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>he</t>
+          <t>prs</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Hebrew</t>
+          <t>Dari</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -70412,14 +70404,14 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70436,12 +70428,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Dravidian (Other)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Dravidian</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -70456,12 +70448,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>inc</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Dravidian</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -70471,14 +70463,14 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70495,12 +70487,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Somali</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Somali</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -70515,12 +70507,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>so</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Somali</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -70530,14 +70522,14 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70554,12 +70546,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Swahili</t>
+          <t>nld</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Swahili</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -70574,12 +70566,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>sw</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Swahili</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -70589,14 +70581,14 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70613,12 +70605,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Amharic</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Amharic</t>
+          <t>English</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -70633,12 +70625,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>am</t>
+          <t>en</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Amharic</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -70648,14 +70640,14 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70672,12 +70664,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>English</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -70692,12 +70684,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>bn</t>
+          <t>en</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -70707,14 +70699,14 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70731,12 +70723,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gujarati</t>
+          <t>Esperanto</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Gujarati</t>
+          <t>Esperanto</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -70751,12 +70743,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>gu</t>
+          <t>eo</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Gujarati</t>
+          <t>Esperanto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -70766,14 +70758,14 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70790,12 +70782,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Urdu</t>
+          <t>Ethiopic</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Urdu</t>
+          <t>Ethiopic</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -70810,12 +70802,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ur</t>
+          <t>gez</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Urdu</t>
+          <t>Ethiopic</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -70825,14 +70817,14 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70849,12 +70841,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lao</t>
+          <t>FAR</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Lao</t>
+          <t>Fataleka</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -70869,12 +70861,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>lo</t>
+          <t>far</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Lao</t>
+          <t>Fataleka</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -70884,14 +70876,14 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70908,12 +70900,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Laotian</t>
+          <t>Faroese</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Laotian</t>
+          <t>Faroese</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -70928,12 +70920,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>lo</t>
+          <t>fo</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Laotian</t>
+          <t>Faroese</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -70943,14 +70935,14 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -70967,12 +70959,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cambodian</t>
+          <t>Farsi</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cambodian</t>
+          <t>Farsi</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -70987,12 +70979,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>km</t>
+          <t>fa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Cambodian</t>
+          <t>Farsi</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -71002,14 +70994,14 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71026,12 +71018,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Armenian</t>
+          <t>Fijian</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Armenian</t>
+          <t>Fijian</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -71046,12 +71038,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>hy</t>
+          <t>fj</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Armenian</t>
+          <t>Fijian</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -71061,14 +71053,14 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71085,12 +71077,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ASL</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Sign language</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -71105,12 +71097,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>sgn</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sign language</t>
+          <t>Filipino</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -71120,14 +71112,14 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71144,12 +71136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sign Language</t>
+          <t>French</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sign language</t>
+          <t>French</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -71164,12 +71156,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>sgn</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sign language</t>
+          <t>French</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -71179,14 +71171,14 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71203,12 +71195,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>sgn</t>
+          <t>Georgian</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sign Language</t>
+          <t>Georgian</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -71223,12 +71215,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>sgn</t>
+          <t>ka</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sign Language</t>
+          <t>Georgian</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -71238,14 +71230,14 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language groupings</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71262,12 +71254,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>German</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>German</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -71280,23 +71272,31 @@
           <t>urn:ietf:bcp:47</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates; und excluded per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71313,12 +71313,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Declined to specify</t>
+          <t>Greek, Modern (1453-)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Declined to specify</t>
+          <t>Modern Greek</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -71331,23 +71331,31 @@
           <t>urn:ietf:bcp:47</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>el</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Modern Greek</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates; und excluded per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71364,12 +71372,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Declined to spec</t>
+          <t>Gujarati</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Declined to spec</t>
+          <t>Gujarati</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -71382,23 +71390,31 @@
           <t>urn:ietf:bcp:47</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>gu</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Gujarati</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates; und excluded per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71415,12 +71431,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>Hebrew</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>Hebrew</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -71433,23 +71449,31 @@
           <t>urn:ietf:bcp:47</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>he</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Hebrew</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates; und excluded per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71466,12 +71490,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -71484,23 +71508,31 @@
           <t>urn:ietf:bcp:47</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates; und excluded per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71517,12 +71549,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>hin</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -71535,23 +71567,31 @@
           <t>urn:ietf:bcp:47</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Excluded from county aggregates; und excluded per survivorship</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71563,37 +71603,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Hungarian</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Hungarian</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>hu</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Hungarian</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -71603,14 +71643,14 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71622,37 +71662,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Igbo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Igbo</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>ig</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Igbo</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -71662,14 +71702,14 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71681,54 +71721,54 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Indonesian</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Indonesian</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>id</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Indonesian</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>rollup</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71740,54 +71780,54 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Italian</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Italian</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>it</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Italian</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>rollup</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71799,54 +71839,54 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Male to Female</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Male to Female</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>rollup</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71858,54 +71898,54 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Female to Male</t>
+          <t>jpn</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Female to Male</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>rollup</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 gender groupings — not Patient.gender_id</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71917,54 +71957,54 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>kar</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Treated as null at master level per county SexID logic</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -71976,54 +72016,54 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Khotanese</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Khotanese</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>kho</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Khotanese</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Treated as null at master level per county SexID logic</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -72035,54 +72075,54 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Korean</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Korean</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Korean</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Treated as null at master level per county SexID logic</t>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
         </is>
       </c>
     </row>
@@ -72094,52 +72134,4480 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SexID</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Unknown/ Other</t>
+          <t>Lao</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Unknown/ Other</t>
+          <t>Lao</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Patient.birth_sex</t>
+          <t>Patient.language</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+          <t>urn:ietf:bcp:47</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>lo</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lao</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>exclude</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Laotian</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Laotian</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>lo</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Laotian</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Latin</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Latin</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>la</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Latin</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Lingala</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lingala</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ln</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Lingala</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Lithuanian</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Lithuanian</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>lt</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Lithuanian</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Macedonian</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Macedonian</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>mk</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Macedonian</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Malay</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Malay</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Malay</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Mam</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Mam</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>mam</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Mam</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Mandingo</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Mandingo</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>mnk</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Mandingo</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Mandarin</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Mandarin</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>cmn</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Mandarin</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Mien</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Mien</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ium</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Mien</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Mongolian</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Mongolian</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>mn</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Mongolian</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Navajo; Navaho</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Navajo; Navaho</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>nv</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Navajo; Navaho</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Nepali</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Nepali</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Nepali</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Oromo</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Oromo</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>om</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Oromo</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Panjabi; Punjabi</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Panjabi; Punjabi</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>pa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Panjabi; Punjabi</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Persian</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Persian</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>fa</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Persian</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Philippine (Other)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Philippine</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>phi</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Philippine</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>pl</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Pushto; Pashto</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Pushto; Pashto</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>ps</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Pushto; Pashto</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Quechua</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Quechua</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>qu</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Quechua</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Romani</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Romani</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>rom</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Romani</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Romanian; Moldavian; Moldovan</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Romanian; Moldavian; Moldovan</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Romanian; Moldavian; Moldovan</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>ru</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>rus</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ru</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Samoan</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Samoan</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>sm</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Samoan</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Serbian</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Serbian</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>sr</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Serbian</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Sign Language</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Sign Language</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>sgn</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sign Language</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>sgn</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Sign Language</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>sgn</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sign Language</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Sinhala; Sinhalese</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sinhala; Sinhalese</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sinhala; Sinhalese</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Slavic (Other)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Slavic</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>sla</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Slavic</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>so</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>spa</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>es</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Sundanese</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Sundanese</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>su</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sundanese</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Swedish</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Swedish</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>sv</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Swedish</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>tl</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>tgl</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>tl</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Tagalog</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Tai (Other)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Tai</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>tai</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Tai</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>ta</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Thai</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Thai</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>th</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Thai</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Tibetan</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Tibetan</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>bo</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Tibetan</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>ti</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Tigrinya</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>ti</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>tir</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>ti</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Tigrigna</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Tonga (Nyasa)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Tonga (Nyasa)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>tog</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Tonga (Nyasa)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Tonga (Tonga Islands)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Tonga (Tonga Islands)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Tonga (Tonga Islands)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>tr</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Turkish</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Twi</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Twi</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Twi</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ukrainian</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Ukrainian</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Ukrainian</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per Table 4 survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per Table 4 survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Urdu</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Urdu</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>ur</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Urdu</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Uzbek</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Uzbek</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>uz</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Uzbek</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>vie</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>vi</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Wolof</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Wolof</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>wo</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Wolof</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Yoruba</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Yoruba</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>yo</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Yoruba</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 4 language detail → BCP 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Declined to specify</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Declined to specify</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per Table 4 survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per Table 4 survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per Table 4 survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Declined to spec</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Declined to spec</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per Table 4 survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Patient.language</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>urn:ietf:bcp:47</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Excluded from county aggregates per Table 4 survivorship</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 SexID — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 SexID — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 SexID — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 SexID — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Male to Female</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Male to Female</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 SexID — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Female to Male</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Female to Male</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>rollup</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>SHIE master-demographics survivorship workbook; Table 4/5/2 SQL; Table 2 SexID — not Patient.gender_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Unknown/ Other</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Unknown/ Other</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Treated as null at master level per county SexID logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Treated as null at master level per county SexID logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Treated as null at master level per county SexID logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>county_master</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SexID</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Patient.birth_sex</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/birthsex</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
         <is>
           <t>Treated as null at master level per county SexID logic</t>
         </is>
